--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_0_0.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/250000/Output_0_0.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10100831.99999656</v>
+        <v>13476767.25690909</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27413131.11299811</v>
+        <v>30789066.36991068</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1806603.604278322</v>
+        <v>-1.398707672358336e-10</v>
       </c>
     </row>
     <row r="11">
@@ -7965,13 +7965,13 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>230.3462332272727</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -8053,10 +8053,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -8120,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -8129,7 +8129,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -8205,13 +8205,13 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>231.2329957552695</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -8275,16 +8275,16 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>137.841438974359</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>142.1340339220183</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>131.3417120833333</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -8293,7 +8293,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -8357,13 +8357,13 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>138.9257839476051</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>127.6855444652332</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -8436,16 +8436,16 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -8512,22 +8512,22 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>137.841438974359</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>142.1340339220183</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>142.5962444444444</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -8594,16 +8594,16 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>127.6855444652332</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -8670,7 +8670,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>220.0898510449805</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -8679,13 +8679,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>231.2329957552695</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -8749,25 +8749,25 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>137.841438974359</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>131.3417120833333</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -8831,16 +8831,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>127.6855444652332</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -8910,19 +8910,19 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>230.3462332272727</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>231.2329957552695</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -8986,22 +8986,22 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>137.841438974359</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>142.1340339220183</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>142.5962444444444</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -9071,13 +9071,13 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>138.9257839476051</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>127.6855444652332</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
@@ -9153,13 +9153,13 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>231.2329957552695</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -9223,10 +9223,10 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>137.841438974359</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -9235,13 +9235,13 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>142.5962444444444</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -9305,16 +9305,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>138.9257839476051</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -9381,16 +9381,16 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>220.0898510449805</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>230.3462332272727</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9463,7 +9463,7 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -9478,7 +9478,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>138.9257839476051</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>127.6855444652332</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -9618,10 +9618,10 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>220.0898510449805</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -9630,7 +9630,7 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -9697,7 +9697,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>137.841438974359</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -9715,7 +9715,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -9779,16 +9779,16 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>138.9257839476051</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>127.6855444652332</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -9861,13 +9861,13 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>230.3462332272727</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -9937,22 +9937,22 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>131.3417120833333</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -10016,7 +10016,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -10025,7 +10025,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -10092,7 +10092,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>220.0898510449805</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -10107,7 +10107,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>231.2329957552695</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -10171,16 +10171,16 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>137.841438974359</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>131.3417120833333</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -10256,13 +10256,13 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>138.9257839476051</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
         <v>0</v>
@@ -10332,16 +10332,16 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>230.3462332272727</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -10408,19 +10408,19 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>137.841438974359</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>142.1340339220183</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>142.5962444444444</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -10566,22 +10566,22 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>220.0898510449805</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>231.2329957552695</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -10648,19 +10648,19 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>131.3417120833333</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -10727,13 +10727,13 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>127.6855444652332</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -10809,10 +10809,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>230.3462332272727</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10891,13 +10891,13 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>131.3417120833333</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -10964,16 +10964,16 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>138.9257839476051</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -11043,19 +11043,19 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>230.3462332272727</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>231.2329957552695</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -11119,25 +11119,25 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>137.841438974359</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>142.1340339220183</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>142.5962444444444</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -11201,7 +11201,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -11210,7 +11210,7 @@
         <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
@@ -11277,22 +11277,22 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>220.0898510449805</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>235.7664149699872</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>229.4130635965909</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>230.0982114216867</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>231.2329957552695</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -11359,22 +11359,22 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>138.5543797798742</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>142.1340339220183</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>142.5962444444444</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>133.9744074143302</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>139.9817740860215</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -11438,7 +11438,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>134.8846762812383</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -11447,7 +11447,7 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>138.4565384518428</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -22537,13 +22537,13 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P2" t="n">
         <v>231.2329957552695</v>
@@ -22625,10 +22625,10 @@
         <v>142.5962444444444</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R3" t="n">
         <v>145.679503963964</v>
@@ -22692,7 +22692,7 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M4" t="n">
         <v>138.9257839476051</v>
@@ -22701,7 +22701,7 @@
         <v>127.6855444652332</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P4" t="n">
         <v>137.7280040491476</v>
@@ -22777,13 +22777,13 @@
         <v>230.3462332272727</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q5" t="n">
         <v>222.3056898744495</v>
@@ -22847,16 +22847,16 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L6" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O6" t="n">
         <v>142.5962444444444</v>
@@ -22865,7 +22865,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R6" t="n">
         <v>145.679503963964</v>
@@ -22929,13 +22929,13 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O7" t="n">
         <v>138.4565384518428</v>
@@ -23008,16 +23008,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M8" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P8" t="n">
         <v>231.2329957552695</v>
@@ -23084,22 +23084,22 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N9" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
         <v>139.9817740860215</v>
@@ -23166,16 +23166,16 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M10" t="n">
         <v>138.9257839476051</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P10" t="n">
         <v>137.7280040491476</v>
@@ -23242,7 +23242,7 @@
         <v>181.0459045266863</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L11" t="n">
         <v>235.7664149699872</v>
@@ -23251,13 +23251,13 @@
         <v>230.3462332272727</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q11" t="n">
         <v>222.3056898744495</v>
@@ -23321,25 +23321,25 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M12" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O12" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R12" t="n">
         <v>145.679503963964</v>
@@ -23403,16 +23403,16 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M13" t="n">
         <v>138.9257839476051</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P13" t="n">
         <v>137.7280040491476</v>
@@ -23482,19 +23482,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q14" t="n">
         <v>222.3056898744495</v>
@@ -23558,22 +23558,22 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N15" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
         <v>139.9817740860215</v>
@@ -23643,13 +23643,13 @@
         <v>134.8846762812383</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P16" t="n">
         <v>137.7280040491476</v>
@@ -23725,13 +23725,13 @@
         <v>230.3462332272727</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O17" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q17" t="n">
         <v>222.3056898744495</v>
@@ -23795,10 +23795,10 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M18" t="n">
         <v>142.1340339220183</v>
@@ -23807,13 +23807,13 @@
         <v>131.3417120833333</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P18" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R18" t="n">
         <v>145.679503963964</v>
@@ -23877,16 +23877,16 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N19" t="n">
         <v>127.6855444652332</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P19" t="n">
         <v>137.7280040491476</v>
@@ -23953,16 +23953,16 @@
         <v>181.0459045266863</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L20" t="n">
         <v>235.7664149699872</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O20" t="n">
         <v>230.0982114216867</v>
@@ -24035,7 +24035,7 @@
         <v>137.841438974359</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
         <v>142.1340339220183</v>
@@ -24050,7 +24050,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R21" t="n">
         <v>145.679503963964</v>
@@ -24114,13 +24114,13 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O22" t="n">
         <v>138.4565384518428</v>
@@ -24190,10 +24190,10 @@
         <v>181.0459045266863</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M23" t="n">
         <v>230.3462332272727</v>
@@ -24202,7 +24202,7 @@
         <v>229.4130635965909</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P23" t="n">
         <v>231.2329957552695</v>
@@ -24269,7 +24269,7 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
         <v>138.5543797798742</v>
@@ -24287,7 +24287,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R24" t="n">
         <v>145.679503963964</v>
@@ -24351,16 +24351,16 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P25" t="n">
         <v>137.7280040491476</v>
@@ -24433,13 +24433,13 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P26" t="n">
         <v>231.2329957552695</v>
@@ -24509,22 +24509,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O27" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R27" t="n">
         <v>145.679503963964</v>
@@ -24588,7 +24588,7 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M28" t="n">
         <v>138.9257839476051</v>
@@ -24597,7 +24597,7 @@
         <v>127.6855444652332</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P28" t="n">
         <v>137.7280040491476</v>
@@ -24664,7 +24664,7 @@
         <v>181.0459045266863</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L29" t="n">
         <v>235.7664149699872</v>
@@ -24679,7 +24679,7 @@
         <v>230.0982114216867</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q29" t="n">
         <v>222.3056898744495</v>
@@ -24743,16 +24743,16 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M30" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O30" t="n">
         <v>142.5962444444444</v>
@@ -24828,13 +24828,13 @@
         <v>134.8846762812383</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N31" t="n">
         <v>127.6855444652332</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P31" t="n">
         <v>137.7280040491476</v>
@@ -24904,16 +24904,16 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P32" t="n">
         <v>231.2329957552695</v>
@@ -24980,19 +24980,19 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N33" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P33" t="n">
         <v>133.9744074143302</v>
@@ -25138,22 +25138,22 @@
         <v>181.0459045266863</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M35" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O35" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q35" t="n">
         <v>222.3056898744495</v>
@@ -25220,19 +25220,19 @@
         <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M36" t="n">
         <v>142.1340339220183</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O36" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q36" t="n">
         <v>139.9817740860215</v>
@@ -25299,13 +25299,13 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M37" t="n">
         <v>138.9257839476051</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>127.6855444652332</v>
       </c>
       <c r="O37" t="n">
         <v>138.4565384518428</v>
@@ -25381,10 +25381,10 @@
         <v>235.7664149699872</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O38" t="n">
         <v>230.0982114216867</v>
@@ -25463,13 +25463,13 @@
         <v>142.1340339220183</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>131.3417120833333</v>
       </c>
       <c r="O39" t="n">
         <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q39" t="n">
         <v>139.9817740860215</v>
@@ -25536,16 +25536,16 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>138.9257839476051</v>
       </c>
       <c r="N40" t="n">
         <v>127.6855444652332</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P40" t="n">
         <v>137.7280040491476</v>
@@ -25615,19 +25615,19 @@
         <v>220.0898510449805</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>230.3462332272727</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q41" t="n">
         <v>222.3056898744495</v>
@@ -25691,25 +25691,25 @@
         <v>126.8376266666667</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L42" t="n">
         <v>138.5543797798742</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N42" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R42" t="n">
         <v>145.679503963964</v>
@@ -25773,7 +25773,7 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M43" t="n">
         <v>138.9257839476051</v>
@@ -25782,7 +25782,7 @@
         <v>127.6855444652332</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P43" t="n">
         <v>137.7280040491476</v>
@@ -25849,22 +25849,22 @@
         <v>181.0459045266863</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>235.7664149699872</v>
       </c>
       <c r="M44" t="n">
         <v>230.3462332272727</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q44" t="n">
         <v>222.3056898744495</v>
@@ -25931,22 +25931,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N45" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R45" t="n">
         <v>145.679503963964</v>
@@ -26010,7 +26010,7 @@
         <v>129.0132581705354</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>134.8846762812383</v>
       </c>
       <c r="M46" t="n">
         <v>138.9257839476051</v>
@@ -26019,7 +26019,7 @@
         <v>127.6855444652332</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>138.4565384518428</v>
       </c>
       <c r="P46" t="n">
         <v>137.7280040491476</v>
@@ -26078,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>127905.0305847206</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="3">
@@ -26086,7 +26086,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>153989.8918785837</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="4">
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>165271.7635381935</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>162251.3096600827</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>229739.4766574488</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>122959.0687388276</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>132233.2011121307</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>138845.9479281348</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>147931.3206009706</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>104773.4548881991</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>160294.2339306133</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>168663.9142413442</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>101046.1400588796</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>224312.8699254378</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
     <row r="16">
@@ -26190,7 +26190,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>222937.0560952137</v>
+        <v>-1.209627953357994e-11</v>
       </c>
     </row>
   </sheetData>
